--- a/2026otopark/bariyerOlcu.xlsx
+++ b/2026otopark/bariyerOlcu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-jcts\2026otopark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAB1F722-A1A7-40F2-89B0-953D2D9708E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A85F8FF-AEF4-426D-9FB2-B13E4AAACB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5730" yWindow="4410" windowWidth="13470" windowHeight="9765" xr2:uid="{4E9E6664-2797-4368-964D-0E9DAA515CF5}"/>
+    <workbookView xWindow="14880" yWindow="1860" windowWidth="13470" windowHeight="13020" xr2:uid="{4E9E6664-2797-4368-964D-0E9DAA515CF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>ef</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>eh dikey</t>
+  </si>
+  <si>
+    <t>motor</t>
   </si>
 </sst>
 </file>
@@ -401,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4EB9B28-C06F-4EF2-9687-AA76B2E2B20E}">
-  <dimension ref="B3:G8"/>
+  <dimension ref="B3:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
@@ -516,6 +519,14 @@
         <v>9</v>
       </c>
     </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>16.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026otopark/bariyerOlcu.xlsx
+++ b/2026otopark/bariyerOlcu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-jcts\2026otopark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A85F8FF-AEF4-426D-9FB2-B13E4AAACB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208D8201-09AF-44FC-AF33-816545DF47C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14880" yWindow="1860" windowWidth="13470" windowHeight="13020" xr2:uid="{4E9E6664-2797-4368-964D-0E9DAA515CF5}"/>
+    <workbookView xWindow="45" yWindow="2145" windowWidth="12390" windowHeight="11295" xr2:uid="{4E9E6664-2797-4368-964D-0E9DAA515CF5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -58,6 +58,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -88,8 +91,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,8 +408,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4EB9B28-C06F-4EF2-9687-AA76B2E2B20E}">
-  <dimension ref="B3:G11"/>
+  <dimension ref="B3:G27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -527,7 +536,152 @@
         <v>16.2</v>
       </c>
     </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>-2.3259999999999999E-3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C16" s="1">
+        <v>2.8639999999999998E-3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>-0.15884999999999999</v>
+      </c>
+      <c r="D18" s="1">
+        <f>C18-C15</f>
+        <v>-0.156524</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>-0.156524</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C19" s="1">
+        <v>0.16839599999999999</v>
+      </c>
+      <c r="D19" s="1">
+        <f>C19-C16</f>
+        <v>0.16553199999999998</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1">
+        <v>0.16553200000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.96708400000000005</v>
+      </c>
+      <c r="D21" s="1">
+        <f>C21-C15</f>
+        <v>0.9694100000000001</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1">
+        <v>0.9694100000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C22" s="1">
+        <v>4.1445600000000002</v>
+      </c>
+      <c r="D22" s="1">
+        <f>C22-C16</f>
+        <v>4.1416960000000005</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1">
+        <v>4.1416959999999996</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0.158527</v>
+      </c>
+      <c r="D24" s="1">
+        <f>C24-C15</f>
+        <v>0.160853</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1">
+        <v>0.160853</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C25" s="1">
+        <v>0.194244</v>
+      </c>
+      <c r="D25" s="1">
+        <f>C25-C16</f>
+        <v>0.19137999999999999</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1">
+        <v>0.19137999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>